--- a/finance/output/SP500_Financial_Metrics_20250429_185617.xlsx
+++ b/finance/output/SP500_Financial_Metrics_20250429_185617.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\finance_script\finance\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{827DB4D1-4200-4DF0-9F77-C407D791380D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04061F6F-E1E5-44AF-BFF3-036D353B34C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13215,7 +13215,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -13276,6 +13276,24 @@
         <bgColor rgb="FFE0E0E0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFE0E0E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor rgb="FFE0E0E0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -13304,7 +13322,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -13318,6 +13336,9 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -14764,7 +14785,7 @@
       <c r="G28" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="H28" s="3" t="s">
+      <c r="H28" s="12" t="s">
         <v>301</v>
       </c>
       <c r="I28" s="3" t="s">
@@ -15297,7 +15318,7 @@
       <c r="G41" t="s">
         <v>440</v>
       </c>
-      <c r="H41" t="s">
+      <c r="H41" s="11" t="s">
         <v>441</v>
       </c>
       <c r="I41" t="s">
@@ -16035,7 +16056,7 @@
       <c r="G59" s="4" t="s">
         <v>620</v>
       </c>
-      <c r="H59" t="s">
+      <c r="H59" s="11" t="s">
         <v>621</v>
       </c>
       <c r="I59" t="s">
@@ -19684,7 +19705,7 @@
       <c r="G148" s="3" t="s">
         <v>1458</v>
       </c>
-      <c r="H148" s="3" t="s">
+      <c r="H148" s="12" t="s">
         <v>1459</v>
       </c>
       <c r="I148" s="3" t="s">
@@ -20240,7 +20261,7 @@
       <c r="A162" s="5" t="s">
         <v>1587</v>
       </c>
-      <c r="B162" s="10" t="s">
+      <c r="B162" s="13" t="s">
         <v>1588</v>
       </c>
       <c r="C162" s="3" t="s">
@@ -24604,7 +24625,7 @@
       <c r="G268" s="4" t="s">
         <v>2522</v>
       </c>
-      <c r="H268" s="3" t="s">
+      <c r="H268" s="12" t="s">
         <v>2523</v>
       </c>
       <c r="I268" s="3" t="s">
@@ -26162,7 +26183,7 @@
       <c r="G306" s="3" t="s">
         <v>2848</v>
       </c>
-      <c r="H306" s="3" t="s">
+      <c r="H306" s="12" t="s">
         <v>2849</v>
       </c>
       <c r="I306" s="3" t="s">
@@ -28294,7 +28315,7 @@
       <c r="G358" s="3" t="s">
         <v>3277</v>
       </c>
-      <c r="H358" s="3" t="s">
+      <c r="H358" s="12" t="s">
         <v>3278</v>
       </c>
       <c r="I358" s="3" t="s">
